--- a/MEME_OUTPUT/direct_meme_out_1_motif5.xlsx
+++ b/MEME_OUTPUT/direct_meme_out_1_motif5.xlsx
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.5564</v>
+        <v>0.5563774490203919</v>
       </c>
     </row>
     <row r="3">
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.5184</v>
+        <v>0.5183926429428228</v>
       </c>
     </row>
     <row r="4">
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.9976</v>
+        <v>0.9974010395841664</v>
       </c>
     </row>
     <row r="5">
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.9998</v>
+        <v>0.9996001599360256</v>
       </c>
     </row>
     <row r="6">
@@ -602,7 +602,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.9898</v>
+        <v>0.9896041583366654</v>
       </c>
     </row>
     <row r="7">
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0.92</v>
+        <v>0.9198320671731307</v>
       </c>
     </row>
     <row r="8">
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0.9576</v>
+        <v>0.9574170331867253</v>
       </c>
     </row>
     <row r="9">
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0.92</v>
+        <v>0.9198320671731307</v>
       </c>
     </row>
     <row r="10">
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0.9896</v>
+        <v>0.9894042383046782</v>
       </c>
     </row>
     <row r="11">
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0.7386</v>
+        <v>0.7385045981607357</v>
       </c>
     </row>
   </sheetData>

--- a/MEME_OUTPUT/direct_meme_out_1_motif5.xlsx
+++ b/MEME_OUTPUT/direct_meme_out_1_motif5.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,15 +446,25 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>full_pattern</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>group1</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>group2</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>full_pattern_html</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>p_value</t>
         </is>
@@ -477,15 +487,25 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>AAAA</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>AAA</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>AAA</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: purple; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: purple; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>0.5563774490203919</v>
       </c>
     </row>
@@ -506,15 +526,25 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>TTTGTTT</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>TTT</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>TTT</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;G&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
         <v>0.5183926429428228</v>
       </c>
     </row>
@@ -535,15 +565,25 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>AAAA</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>AA</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
         <v>0.9974010395841664</v>
       </c>
     </row>
@@ -564,7 +604,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>TT</t>
+          <t>TTATATGAAAATT</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -572,7 +612,17 @@
           <t>TT</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;ATATGAAAA&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
         <v>0.9996001599360256</v>
       </c>
     </row>
@@ -593,7 +643,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>TT</t>
+          <t>TTATATGAAAATTT</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -601,7 +651,17 @@
           <t>TT</t>
         </is>
       </c>
-      <c r="G6" t="n">
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;ATATGAAAAT&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
         <v>0.9896041583366654</v>
       </c>
     </row>
@@ -622,7 +682,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>TT</t>
+          <t>TTATATGAAAATTTGTT</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -630,7 +690,17 @@
           <t>TT</t>
         </is>
       </c>
-      <c r="G7" t="n">
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;ATATGAAAATTTG&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
         <v>0.9198320671731307</v>
       </c>
     </row>
@@ -651,7 +721,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>TT</t>
+          <t>TTGTT</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -659,7 +729,17 @@
           <t>TT</t>
         </is>
       </c>
-      <c r="G8" t="n">
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;G&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
         <v>0.9574170331867253</v>
       </c>
     </row>
@@ -680,7 +760,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>TT</t>
+          <t>TTATATGAAAATTTGTTT</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -688,7 +768,17 @@
           <t>TT</t>
         </is>
       </c>
-      <c r="G9" t="n">
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;ATATGAAAATTTGT&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
         <v>0.9198320671731307</v>
       </c>
     </row>
@@ -709,7 +799,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>TT</t>
+          <t>TTTGTTT</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -717,7 +807,17 @@
           <t>TT</t>
         </is>
       </c>
-      <c r="G10" t="n">
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;TGT&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
         <v>0.9894042383046782</v>
       </c>
     </row>
@@ -738,7 +838,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>TT</t>
+          <t>TTT</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -746,7 +846,17 @@
           <t>TT</t>
         </is>
       </c>
-      <c r="G11" t="n">
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>TT</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: purple; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
         <v>0.7385045981607357</v>
       </c>
     </row>
